--- a/Stitch Calcs.xlsx
+++ b/Stitch Calcs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Claire\Local Git Code\Embroidery Machine\CNC-Embroidery-Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C91DCB-EDF5-439A-86F7-E2714BE086B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BED95CE-BA94-4C99-AC63-B298740D1A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1290" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{ACDFC889-B2AC-4DD9-89C7-9C66E4575298}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{ACDFC889-B2AC-4DD9-89C7-9C66E4575298}"/>
   </bookViews>
   <sheets>
     <sheet name="PW to Freq" sheetId="1" r:id="rId1"/>
     <sheet name="Accel and Vmax" sheetId="2" r:id="rId2"/>
-    <sheet name="Stitch Period" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
+    <sheet name="Graphing " sheetId="7" r:id="rId3"/>
+    <sheet name="Stitch Period" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>Period (s)</t>
   </si>
@@ -665,9 +665,9 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1352486" cy="636328"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="1352486" cy="658001"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -682,7 +682,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="5895975" y="1757362"/>
-              <a:ext cx="1352486" cy="636328"/>
+              <a:ext cx="1352486" cy="658001"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -764,14 +764,14 @@
                         </m:sSub>
                       </m:num>
                       <m:den>
-                        <m:sSub>
-                          <m:sSubPr>
+                        <m:sSubSup>
+                          <m:sSubSupPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-CA" sz="2000" b="0" i="1">
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
-                          </m:sSubPr>
+                          </m:sSubSupPr>
                           <m:e>
                             <m:r>
                               <a:rPr lang="en-CA" sz="2000" b="0" i="1">
@@ -788,7 +788,15 @@
                               <m:t>𝑡</m:t>
                             </m:r>
                           </m:sub>
-                        </m:sSub>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSubSup>
                       </m:den>
                     </m:f>
                   </m:oMath>
@@ -799,7 +807,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -814,7 +822,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="5895975" y="1757362"/>
-              <a:ext cx="1352486" cy="636328"/>
+              <a:ext cx="1352486" cy="658001"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -841,11 +849,36 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-CA" sz="2000" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑎=4.5∗𝑑_𝑡/𝑡_𝑡 </a:t>
+                <a:t>𝑎=4.5∗𝑑_𝑡/(𝑡</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-CA" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑡^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-CA" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> )</a:t>
               </a:r>
               <a:endParaRPr lang="en-CA" sz="2000"/>
             </a:p>
@@ -1251,6 +1284,1470 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4035207" cy="1880515"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68135C8F-218F-04CC-8319-475875A3D2DD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6381750" y="228600"/>
+              <a:ext cx="4035207" cy="1880515"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑣</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:begChr m:val="{"/>
+                        <m:endChr m:val=""/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:eqArr>
+                          <m:eqArrPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:eqArrPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑎</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  0≤</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>≤</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                          </m:e>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑣</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑚𝑎𝑥</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>&lt;</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>≤</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑎𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑎</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>&lt;</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>≤</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:eqArr>
+                      </m:e>
+                    </m:d>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68135C8F-218F-04CC-8319-475875A3D2DD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6381750" y="228600"/>
+              <a:ext cx="4035207" cy="1880515"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑣(𝑡)={█(𝑎</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑡,  0≤𝑡≤𝑡_𝑡/3@</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑣_𝑚𝑎𝑥,  𝑡_𝑡/3&lt;𝑡≤2/3 𝑡_𝑡@−𝑎</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑡+𝑎𝑡_𝑡,  2/3 𝑡_𝑡&lt;𝑡≤𝑡_𝑡 )┤</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5730095" cy="1984389"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D986E4A5-E520-2D80-193C-550B406D018A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6372225" y="2462212"/>
+              <a:ext cx="5730095" cy="1984389"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑠</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:begChr m:val="{"/>
+                        <m:endChr m:val=""/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:eqArr>
+                          <m:eqArrPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:eqArrPr>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑎</m:t>
+                                </m:r>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  0≤</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>≤</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                          </m:e>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑣</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑚𝑎𝑥</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>∙</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑣</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑚𝑎𝑥</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>∙</m:t>
+                                </m:r>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>6</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>&lt;</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>≤</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑎</m:t>
+                                </m:r>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑎</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>∙</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑠</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑎</m:t>
+                                </m:r>
+                                <m:sSubSup>
+                                  <m:sSubSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSubSup>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>&lt;</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>≤</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:eqArr>
+                      </m:e>
+                    </m:d>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D986E4A5-E520-2D80-193C-550B406D018A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6372225" y="2462212"/>
+              <a:ext cx="5730095" cy="1984389"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑠(𝑡)={█((𝑎𝑡^2)/2,  0≤𝑡≤𝑡_𝑡/3@𝑣_𝑚𝑎𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∙</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑡−(𝑣_𝑚𝑎𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∙𝑡)/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>6,  𝑡_𝑡/3&lt;𝑡≤2/3 𝑡_𝑡@−(𝑎𝑡^2)/2+𝑎𝑡_𝑡</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∙𝑡+𝑠_𝑡−(𝑎𝑡_𝑡^2)/2,  2/3 𝑡_𝑡&lt;𝑡≤𝑡_𝑡 )┤</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DF0C6F8F-B324-4861-84EE-91AF5FE25959}" name="Period_Calc" displayName="Period_Calc" ref="A1:D11" totalsRowShown="0">
   <autoFilter ref="A1:D11" xr:uid="{DF0C6F8F-B324-4861-84EE-91AF5FE25959}"/>
@@ -2232,6 +3729,244 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF8ABD8-8317-4642-B491-390AE8B1FEFE}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <f t="shared" ref="B2:B9" si="0">POWER(A2,-1)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C2" s="1">
+        <f t="shared" ref="C2:C9" si="1">(1.5*0.003/B2)</f>
+        <v>1.3500000000000002E-2</v>
+      </c>
+      <c r="D2" s="1">
+        <f t="shared" ref="D2:D9" si="2">(1.5 * 300 /B2)</f>
+        <v>1350</v>
+      </c>
+      <c r="E2" s="1">
+        <f t="shared" ref="E2:E9" si="3">(4.5 * 0.003/POWER(B2,2))</f>
+        <v>0.12150000000000001</v>
+      </c>
+      <c r="F2" s="1">
+        <f t="shared" ref="F2:F9" si="4">(4.5*300/POWER(B2,2))</f>
+        <v>12150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" si="1"/>
+        <v>1.8000000000000002E-2</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" si="2"/>
+        <v>1800</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" si="3"/>
+        <v>0.216</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="4"/>
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="C4" s="1">
+        <f>(1.5*0.003/B4)</f>
+        <v>2.2500000000000003E-2</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="2"/>
+        <v>2250</v>
+      </c>
+      <c r="E4" s="1">
+        <f>(4.5 * 0.003/POWER(B4,2))</f>
+        <v>0.33749999999999991</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="4"/>
+        <v>33749.999999999993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="1"/>
+        <v>2.7000000000000003E-2</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="2"/>
+        <v>2700</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="3"/>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="4"/>
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="1"/>
+        <v>3.1500000000000007E-2</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="2"/>
+        <v>3150</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="3"/>
+        <v>0.66150000000000009</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="4"/>
+        <v>66150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
+        <v>3.6000000000000004E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="2"/>
+        <v>3600</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="3"/>
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="4"/>
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
+        <v>4.0500000000000008E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="2"/>
+        <v>4050</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="3"/>
+        <v>1.0935000000000001</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="4"/>
+        <v>109350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
+        <v>4.5000000000000005E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="2"/>
+        <v>4500</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="3"/>
+        <v>1.3499999999999996</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="4"/>
+        <v>134999.99999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BBB5E9-8FB7-45F6-ABE1-EDC3636E8964}">
   <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2584,13 +4319,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33184B55-B6C4-4432-943A-B67817C8BC8C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Stitch Calcs.xlsx
+++ b/Stitch Calcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Claire\Local Git Code\Embroidery Machine\CNC-Embroidery-Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BED95CE-BA94-4C99-AC63-B298740D1A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F60D02-DF51-4CE3-9696-19858F27FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{ACDFC889-B2AC-4DD9-89C7-9C66E4575298}"/>
   </bookViews>
@@ -2745,6 +2745,50 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>46950</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>58015</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8484639-3B9D-F90E-C485-EF2DCB840ECD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="95250" y="2085976"/>
+          <a:ext cx="5400000" cy="3153639"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/Stitch Calcs.xlsx
+++ b/Stitch Calcs.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Claire\Local Git Code\Embroidery Machine\CNC-Embroidery-Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F60D02-DF51-4CE3-9696-19858F27FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10492051-BAA1-44D1-A178-49A747677F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{ACDFC889-B2AC-4DD9-89C7-9C66E4575298}"/>
+    <workbookView xWindow="-28920" yWindow="-1290" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{ACDFC889-B2AC-4DD9-89C7-9C66E4575298}"/>
   </bookViews>
   <sheets>
     <sheet name="PW to Freq" sheetId="1" r:id="rId1"/>
     <sheet name="Accel and Vmax" sheetId="2" r:id="rId2"/>
     <sheet name="Graphing " sheetId="7" r:id="rId3"/>
-    <sheet name="Stitch Period" sheetId="3" r:id="rId4"/>
+    <sheet name="time" sheetId="8" r:id="rId4"/>
+    <sheet name="Stitch Period" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +39,67 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Claire</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{F6A07338-C6E4-42DE-A22F-9BCCECAA979D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Claire:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+x=(-b+SQRT(b^2-4ac))/2a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{6765EFB1-BDD9-431C-AC6F-8BD6E9E13A60}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Claire:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+x=(-b-SQRT(b^2-4ac))/2a
+out of range</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>Period (s)</t>
   </si>
@@ -274,18 +334,44 @@
   <si>
     <t xml:space="preserve">Formulas and image: https://www.linearmotiontips.com/how-to-calculate-velocity/ </t>
   </si>
+  <si>
+    <t>displacement (s)</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>t_t</t>
+  </si>
+  <si>
+    <t>s_t</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>t+</t>
+  </si>
+  <si>
+    <t>t-</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="##0.000E+0"/>
     <numFmt numFmtId="165" formatCode="##0E+0"/>
     <numFmt numFmtId="166" formatCode="##0.0000E+0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="##0.00E+0"/>
+    <numFmt numFmtId="169" formatCode="0.E+00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,13 +395,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -330,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -343,6 +454,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,8 +781,8 @@
       <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1352486" cy="658001"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -807,7 +922,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1288,10 +1403,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4035207" cy="1880515"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1309,7 +1424,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6381750" y="228600"/>
+              <a:off x="5705475" y="266700"/>
               <a:ext cx="4035207" cy="1880515"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1337,6 +1452,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1814,7 +1930,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6381750" y="228600"/>
+              <a:off x="5705475" y="266700"/>
               <a:ext cx="4035207" cy="1880515"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1842,6 +1958,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="2000" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1859,14 +1976,14 @@
                 <a:rPr lang="en-US" sz="2000" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑣_𝑚𝑎𝑥,  𝑡_𝑡/3&lt;𝑡≤2/3 𝑡_𝑡@−𝑎</a:t>
+                <a:t>𝑣_𝑚𝑎𝑥,  𝑡_𝑡/3&lt;𝑡≤2/3 𝑡_𝑡@−𝑎𝑡</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" sz="2000" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑡+𝑎𝑡_𝑡,  2/3 𝑡_𝑡&lt;𝑡≤𝑡_𝑡 )┤</a:t>
+                <a:t>+𝑎𝑡_𝑡,  2/3 𝑡_𝑡&lt;𝑡≤𝑡_𝑡 )┤</a:t>
               </a:r>
               <a:endParaRPr lang="en-CA" sz="2000"/>
             </a:p>
@@ -1878,10 +1995,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>138112</xdr:rowOff>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5730095" cy="1984389"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1899,7 +2016,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6372225" y="2462212"/>
+              <a:off x="5524500" y="2443162"/>
               <a:ext cx="5730095" cy="1984389"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1927,6 +2044,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2181,13 +2299,34 @@
                                   </a:rPr>
                                   <m:t>∙</m:t>
                                 </m:r>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑡</m:t>
-                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
                               </m:num>
                               <m:den>
                                 <m:r>
@@ -2670,7 +2809,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6372225" y="2462212"/>
+              <a:off x="5524500" y="2443162"/>
               <a:ext cx="5730095" cy="1984389"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2698,6 +2837,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="2000" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2722,7 +2862,7 @@
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>∙𝑡)/</a:t>
+                <a:t>∙𝑡_𝑡)/</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" sz="2000" b="0" i="0">
@@ -2789,7 +2929,2180 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4143891" cy="2180597"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6BE9C1B-05A1-421C-90BA-C9C0C798460B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12201525" y="2676525"/>
+              <a:ext cx="4143891" cy="2180597"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑠</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:begChr m:val="{"/>
+                        <m:endChr m:val=""/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:eqArr>
+                          <m:eqArrPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:eqArrPr>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                                <m:sSubSup>
+                                  <m:sSubSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSubSup>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑎</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑏</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>−9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                                <m:sSubSup>
+                                  <m:sSubSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSubSup>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>5</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑠</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑐</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:eqArr>
+                      </m:e>
+                    </m:d>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6BE9C1B-05A1-421C-90BA-C9C0C798460B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12201525" y="2676525"/>
+              <a:ext cx="4143891" cy="2180597"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑠(𝑡)={█((9𝑠_𝑡 𝑡^2)/(4𝑡_𝑡^2 ),  𝑡_𝑎@(3𝑠_𝑡 𝑡)/(2𝑡_𝑡 )−𝑠_𝑡/4,  𝑡_𝑏@(−9𝑠_𝑡 𝑡^2)/(4𝑡_𝑡^2 )+(9𝑠_𝑡 𝑡)/(2𝑡_𝑡 )−5/4 𝑠_𝑡,  𝑡_𝑐</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> )┤</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3317960" cy="2141612"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FC82178-60E6-4A20-BCB8-5362A96A5E31}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12144375" y="409575"/>
+              <a:ext cx="3317960" cy="2141612"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑣</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:begChr m:val="{"/>
+                        <m:endChr m:val=""/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:eqArr>
+                          <m:eqArrPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:eqArrPr>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                                <m:sSubSup>
+                                  <m:sSubSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSubSup>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑎</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑏</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>∙</m:t>
+                            </m:r>
+                            <m:d>
+                              <m:dPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:dPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>1−</m:t>
+                                </m:r>
+                                <m:f>
+                                  <m:fPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:fPr>
+                                  <m:num>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:num>
+                                  <m:den>
+                                    <m:sSub>
+                                      <m:sSubPr>
+                                        <m:ctrlPr>
+                                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                          </a:rPr>
+                                        </m:ctrlPr>
+                                      </m:sSubPr>
+                                      <m:e>
+                                        <m:r>
+                                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                          </a:rPr>
+                                          <m:t>𝑡</m:t>
+                                        </m:r>
+                                      </m:e>
+                                      <m:sub>
+                                        <m:r>
+                                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                          </a:rPr>
+                                          <m:t>𝑡</m:t>
+                                        </m:r>
+                                      </m:sub>
+                                    </m:sSub>
+                                  </m:den>
+                                </m:f>
+                              </m:e>
+                            </m:d>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑐</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:eqArr>
+                      </m:e>
+                    </m:d>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FC82178-60E6-4A20-BCB8-5362A96A5E31}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12144375" y="409575"/>
+              <a:ext cx="3317960" cy="2141612"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑣(𝑡)={█((9𝑠_𝑡 𝑡)/(2𝑡_𝑡^2 ),  𝑡_𝑎</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>@(3𝑠_𝑡)/〖2𝑡〗_𝑡 ,  𝑡_𝑏@(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>9𝑠_𝑡)/(2𝑡_𝑡 )</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∙(1−𝑡/𝑡_𝑡 ),  𝑡_𝑐 )┤</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4143891" cy="2180597"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC61F18-59F9-4264-A1D7-7CAF621C26DF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9915525" y="1047750"/>
+              <a:ext cx="4143891" cy="2180597"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑠</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:begChr m:val="{"/>
+                        <m:endChr m:val=""/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:eqArr>
+                          <m:eqArrPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:eqArrPr>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                                <m:sSubSup>
+                                  <m:sSubSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSubSup>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑎</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>3</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑏</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>−9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                                <m:sSubSup>
+                                  <m:sSubSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSubSup>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>9</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑠</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑡</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:den>
+                            </m:f>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:f>
+                              <m:fPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>5</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑠</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,  </m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="2000" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑐</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:eqArr>
+                      </m:e>
+                    </m:d>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC61F18-59F9-4264-A1D7-7CAF621C26DF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9915525" y="1047750"/>
+              <a:ext cx="4143891" cy="2180597"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑠(𝑡)={█((9𝑠_𝑡 𝑡^2)/(4𝑡_𝑡^2 ),  𝑡_𝑎@(3𝑠_𝑡 𝑡)/(2𝑡_𝑡 )−𝑠_𝑡/4,  𝑡_𝑏@(−9𝑠_𝑡 𝑡^2)/(4𝑡_𝑡^2 )+(9𝑠_𝑡 𝑡)/(2𝑡_𝑡 )−5/4 𝑠_𝑡,  𝑡_𝑐</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> )┤</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-CA" sz="2000"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4011,6 +6324,1363 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E34B54-E10F-431F-887C-7CAFC77ACC6C}">
+  <dimension ref="A1:L77"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>2.2499999999999998E-3</v>
+      </c>
+      <c r="B2" s="3">
+        <f>(-5*$I$2/4)-A2</f>
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="C2" s="10">
+        <f>(-$L$2+SQRT(POWER($L$2,2)-(4*$K$2*B2)))/(2*$K$2)</f>
+        <v>0.22222222222222213</v>
+      </c>
+      <c r="D2" s="11">
+        <f>(-$L$2-SQRT(POWER($L$2,2)-(4*$K$2*B2)))/(2*$K$2)</f>
+        <v>0.44444444444444464</v>
+      </c>
+      <c r="H2">
+        <f>POWER(3,-1)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I2" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K2" s="3">
+        <f>(-9/4)*($I$2/POWER($H$2,2))</f>
+        <v>-6.0750000000000005E-2</v>
+      </c>
+      <c r="L2" s="3">
+        <f>(9/2)*($I$2/$H$2)</f>
+        <v>4.0500000000000008E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2.2599999999999999E-3</v>
+      </c>
+      <c r="B3" s="3">
+        <f t="shared" ref="B3:B66" si="0">(-5*$I$2/4)-A3</f>
+        <v>-6.0099999999999997E-3</v>
+      </c>
+      <c r="C3" s="10">
+        <f t="shared" ref="C3:C66" si="1">(-$L$2+SQRT(POWER($L$2,2)-(4*$K$2*B3)))/(2*$K$2)</f>
+        <v>0.22296544869813806</v>
+      </c>
+      <c r="D3" s="11">
+        <f t="shared" ref="D3:D66" si="2">(-$L$2-SQRT(POWER($L$2,2)-(4*$K$2*B3)))/(2*$K$2)</f>
+        <v>0.44370121796852868</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>2.2699999999999999E-3</v>
+      </c>
+      <c r="B4" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0199999999999993E-3</v>
+      </c>
+      <c r="C4" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22371371417074987</v>
+      </c>
+      <c r="D4" s="11">
+        <f t="shared" si="2"/>
+        <v>0.44295295249591687</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>2.2799999999999999E-3</v>
+      </c>
+      <c r="B5" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0299999999999998E-3</v>
+      </c>
+      <c r="C5" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22446712254296977</v>
+      </c>
+      <c r="D5" s="11">
+        <f t="shared" si="2"/>
+        <v>0.44219954412369694</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>2.2899999999999999E-3</v>
+      </c>
+      <c r="B6" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0400000000000002E-3</v>
+      </c>
+      <c r="C6" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22522578133832269</v>
+      </c>
+      <c r="D6" s="11">
+        <f t="shared" si="2"/>
+        <v>0.44144088532834408</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>2.3E-3</v>
+      </c>
+      <c r="B7" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0499999999999998E-3</v>
+      </c>
+      <c r="C7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22598980188007811</v>
+      </c>
+      <c r="D7" s="11">
+        <f t="shared" si="2"/>
+        <v>0.44067686478658857</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>2.31E-3</v>
+      </c>
+      <c r="B8" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0599999999999994E-3</v>
+      </c>
+      <c r="C8" s="10">
+        <f t="shared" si="1"/>
+        <v>0.2267592994819394</v>
+      </c>
+      <c r="D8" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43990736718472734</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>2.32E-3</v>
+      </c>
+      <c r="B9" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0699999999999999E-3</v>
+      </c>
+      <c r="C9" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22753439365121692</v>
+      </c>
+      <c r="D9" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43913227301544983</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>2.33E-3</v>
+      </c>
+      <c r="B10" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0800000000000003E-3</v>
+      </c>
+      <c r="C10" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22831520830549751</v>
+      </c>
+      <c r="D10" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43835145836116923</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>2.3400000000000001E-3</v>
+      </c>
+      <c r="B11" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0899999999999999E-3</v>
+      </c>
+      <c r="C11" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22910187200392365</v>
+      </c>
+      <c r="D11" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43756479466274312</v>
+      </c>
+      <c r="K11" s="3">
+        <f>POWER($L$2,2)-4*$K$2*B2</f>
+        <v>1.8225000000000055E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>2.3500000000000001E-3</v>
+      </c>
+      <c r="B12" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.0999999999999995E-3</v>
+      </c>
+      <c r="C12" s="10">
+        <f t="shared" si="1"/>
+        <v>0.22989451819430395</v>
+      </c>
+      <c r="D12" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43677214847236279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>2.3600000000000001E-3</v>
+      </c>
+      <c r="B13" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.11E-3</v>
+      </c>
+      <c r="C13" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23069328547739973</v>
+      </c>
+      <c r="D13" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43597338118926698</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>2.3700000000000001E-3</v>
+      </c>
+      <c r="B14" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1200000000000004E-3</v>
+      </c>
+      <c r="C14" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23149831788987013</v>
+      </c>
+      <c r="D14" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43516834877679661</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>2.3800000000000002E-3</v>
+      </c>
+      <c r="B15" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.13E-3</v>
+      </c>
+      <c r="C15" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23230976520751204</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43435690145915473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>2.3900000000000002E-3</v>
+      </c>
+      <c r="B16" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1399999999999996E-3</v>
+      </c>
+      <c r="C16" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23312778327060216</v>
+      </c>
+      <c r="D16" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43353888339606461</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="B17" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1499999999999992E-3</v>
+      </c>
+      <c r="C17" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23395253433334254</v>
+      </c>
+      <c r="D17" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43271413233332423</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>2.4099999999999998E-3</v>
+      </c>
+      <c r="B18" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1599999999999997E-3</v>
+      </c>
+      <c r="C18" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23478418743962895</v>
+      </c>
+      <c r="D18" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43188247922703776</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>2.4199999999999998E-3</v>
+      </c>
+      <c r="B19" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1700000000000001E-3</v>
+      </c>
+      <c r="C19" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23562291882760791</v>
+      </c>
+      <c r="D19" s="11">
+        <f t="shared" si="2"/>
+        <v>0.4310437478390588</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>2.4299999999999999E-3</v>
+      </c>
+      <c r="B20" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1799999999999997E-3</v>
+      </c>
+      <c r="C20" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23646891236576267</v>
+      </c>
+      <c r="D20" s="11">
+        <f t="shared" si="2"/>
+        <v>0.43019775430090407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>2.4399999999999999E-3</v>
+      </c>
+      <c r="B21" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1899999999999993E-3</v>
+      </c>
+      <c r="C21" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23732236002358709</v>
+      </c>
+      <c r="D21" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42934430664307965</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>2.4499999999999999E-3</v>
+      </c>
+      <c r="B22" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.1999999999999998E-3</v>
+      </c>
+      <c r="C22" s="10">
+        <f t="shared" si="1"/>
+        <v>0.23818346238025814</v>
+      </c>
+      <c r="D22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42848320428640857</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>2.4599999999999999E-3</v>
+      </c>
+      <c r="B23" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2100000000000002E-3</v>
+      </c>
+      <c r="C23" s="10">
+        <f t="shared" si="1"/>
+        <v>0.2390524291751269</v>
+      </c>
+      <c r="D23" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42761423749153987</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>2.47E-3</v>
+      </c>
+      <c r="B24" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2199999999999998E-3</v>
+      </c>
+      <c r="C24" s="10">
+        <f t="shared" si="1"/>
+        <v>0.2399294799043073</v>
+      </c>
+      <c r="D24" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42673718676235944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>2.48E-3</v>
+      </c>
+      <c r="B25" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2299999999999994E-3</v>
+      </c>
+      <c r="C25" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24081484446817167</v>
+      </c>
+      <c r="D25" s="11">
+        <f t="shared" si="2"/>
+        <v>0.4258518221984951</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>2.49E-3</v>
+      </c>
+      <c r="B26" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2399999999999999E-3</v>
+      </c>
+      <c r="C26" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24170876387516291</v>
+      </c>
+      <c r="D26" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42495790279150381</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="B27" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2500000000000003E-3</v>
+      </c>
+      <c r="C27" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24261149100803031</v>
+      </c>
+      <c r="D27" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42405517565863643</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>2.5100000000000001E-3</v>
+      </c>
+      <c r="B28" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2599999999999999E-3</v>
+      </c>
+      <c r="C28" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24352329145939136</v>
+      </c>
+      <c r="D28" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42314337520727541</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>2.5200000000000001E-3</v>
+      </c>
+      <c r="B29" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2699999999999995E-3</v>
+      </c>
+      <c r="C29" s="10">
+        <f t="shared" si="1"/>
+        <v>0.2444444444444443</v>
+      </c>
+      <c r="D29" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42222222222222244</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>2.5300000000000001E-3</v>
+      </c>
+      <c r="B30" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.28E-3</v>
+      </c>
+      <c r="C30" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24537524379971903</v>
+      </c>
+      <c r="D30" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42129142286694771</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>2.5400000000000002E-3</v>
+      </c>
+      <c r="B31" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.2900000000000005E-3</v>
+      </c>
+      <c r="C31" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24631599907799451</v>
+      </c>
+      <c r="D31" s="11">
+        <f t="shared" si="2"/>
+        <v>0.42035066758867223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>2.5500000000000002E-3</v>
+      </c>
+      <c r="B32" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3E-3</v>
+      </c>
+      <c r="C32" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24726703675094613</v>
+      </c>
+      <c r="D32" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41939962991572061</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>2.5600000000000002E-3</v>
+      </c>
+      <c r="B33" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3099999999999996E-3</v>
+      </c>
+      <c r="C33" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24822870153276974</v>
+      </c>
+      <c r="D33" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41843796513389697</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>2.5699999999999998E-3</v>
+      </c>
+      <c r="B34" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3199999999999992E-3</v>
+      </c>
+      <c r="C34" s="10">
+        <f t="shared" si="1"/>
+        <v>0.24920135783999572</v>
+      </c>
+      <c r="D34" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41746530882667104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>2.5799999999999998E-3</v>
+      </c>
+      <c r="B35" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3299999999999997E-3</v>
+      </c>
+      <c r="C35" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25018539140502333</v>
+      </c>
+      <c r="D35" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41648127526164347</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>2.5899999999999999E-3</v>
+      </c>
+      <c r="B36" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3400000000000001E-3</v>
+      </c>
+      <c r="C36" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25118121106363378</v>
+      </c>
+      <c r="D36" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41548545560303296</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="B37" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3499999999999997E-3</v>
+      </c>
+      <c r="C37" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25218925073997517</v>
+      </c>
+      <c r="D37" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41447741592669157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>2.6099999999999999E-3</v>
+      </c>
+      <c r="B38" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3599999999999993E-3</v>
+      </c>
+      <c r="C38" s="10">
+        <f t="shared" si="1"/>
+        <v>0.2532099716563555</v>
+      </c>
+      <c r="D38" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41345669501031124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>2.6199999999999999E-3</v>
+      </c>
+      <c r="B39" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3699999999999998E-3</v>
+      </c>
+      <c r="C39" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25424386479976785</v>
+      </c>
+      <c r="D39" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41242280186689895</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>2.63E-3</v>
+      </c>
+      <c r="B40" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3800000000000003E-3</v>
+      </c>
+      <c r="C40" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25529145368257211</v>
+      </c>
+      <c r="D40" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41137521298409463</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>2.64E-3</v>
+      </c>
+      <c r="B41" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3899999999999998E-3</v>
+      </c>
+      <c r="C41" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25635329744138308</v>
+      </c>
+      <c r="D41" s="11">
+        <f t="shared" si="2"/>
+        <v>0.41031336922528366</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>2.65E-3</v>
+      </c>
+      <c r="B42" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.3999999999999994E-3</v>
+      </c>
+      <c r="C42" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25742999432622499</v>
+      </c>
+      <c r="D42" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40923667234044175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>2.66E-3</v>
+      </c>
+      <c r="B43" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4099999999999999E-3</v>
+      </c>
+      <c r="C43" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25852218564176221</v>
+      </c>
+      <c r="D43" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40814448102490453</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>2.6700000000000001E-3</v>
+      </c>
+      <c r="B44" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4200000000000004E-3</v>
+      </c>
+      <c r="C44" s="10">
+        <f t="shared" si="1"/>
+        <v>0.25963056021432435</v>
+      </c>
+      <c r="D44" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40703610645234239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>2.6800000000000001E-3</v>
+      </c>
+      <c r="B45" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.43E-3</v>
+      </c>
+      <c r="C45" s="10">
+        <f t="shared" si="1"/>
+        <v>0.26075585947309082</v>
+      </c>
+      <c r="D45" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40591080719357592</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>2.6900000000000001E-3</v>
+      </c>
+      <c r="B46" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4399999999999995E-3</v>
+      </c>
+      <c r="C46" s="10">
+        <f t="shared" si="1"/>
+        <v>0.2618988832519038</v>
+      </c>
+      <c r="D46" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40476778341476294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="B47" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.45E-3</v>
+      </c>
+      <c r="C47" s="10">
+        <f t="shared" si="1"/>
+        <v>0.26306049644070245</v>
+      </c>
+      <c r="D47" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40360617022596429</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>2.7100000000000002E-3</v>
+      </c>
+      <c r="B48" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4600000000000005E-3</v>
+      </c>
+      <c r="C48" s="10">
+        <f t="shared" si="1"/>
+        <v>0.26424163664378636</v>
+      </c>
+      <c r="D48" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40242503002288038</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>2.7200000000000002E-3</v>
+      </c>
+      <c r="B49" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4700000000000001E-3</v>
+      </c>
+      <c r="C49" s="10">
+        <f t="shared" si="1"/>
+        <v>0.26544332303769103</v>
+      </c>
+      <c r="D49" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40122334362897571</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>2.7299999999999998E-3</v>
+      </c>
+      <c r="B50" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4799999999999996E-3</v>
+      </c>
+      <c r="C50" s="10">
+        <f t="shared" si="1"/>
+        <v>0.26666666666666639</v>
+      </c>
+      <c r="D50" s="11">
+        <f t="shared" si="2"/>
+        <v>0.40000000000000036</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>2.7399999999999998E-3</v>
+      </c>
+      <c r="B51" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4899999999999992E-3</v>
+      </c>
+      <c r="C51" s="10">
+        <f t="shared" si="1"/>
+        <v>0.26791288247164524</v>
+      </c>
+      <c r="D51" s="11">
+        <f t="shared" si="2"/>
+        <v>0.3987537841950215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>2.7499999999999998E-3</v>
+      </c>
+      <c r="B52" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4999999999999997E-3</v>
+      </c>
+      <c r="C52" s="10">
+        <f t="shared" si="1"/>
+        <v>0.26918330342337471</v>
+      </c>
+      <c r="D52" s="11">
+        <f t="shared" si="2"/>
+        <v>0.39748336324329203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>2.7599999999999999E-3</v>
+      </c>
+      <c r="B53" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5100000000000002E-3</v>
+      </c>
+      <c r="C53" s="10">
+        <f t="shared" si="1"/>
+        <v>0.27047939722786229</v>
+      </c>
+      <c r="D53" s="11">
+        <f t="shared" si="2"/>
+        <v>0.39618726943880445</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>2.7699999999999999E-3</v>
+      </c>
+      <c r="B54" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5199999999999998E-3</v>
+      </c>
+      <c r="C54" s="10">
+        <f t="shared" si="1"/>
+        <v>0.27180278620060666</v>
+      </c>
+      <c r="D54" s="11">
+        <f t="shared" si="2"/>
+        <v>0.39486388046606008</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>2.7799999999999999E-3</v>
+      </c>
+      <c r="B55" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5299999999999993E-3</v>
+      </c>
+      <c r="C55" s="10">
+        <f t="shared" si="1"/>
+        <v>0.27315527107677035</v>
+      </c>
+      <c r="D55" s="11">
+        <f t="shared" si="2"/>
+        <v>0.3935113955898964</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>2.7899999999999999E-3</v>
+      </c>
+      <c r="B56" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5399999999999998E-3</v>
+      </c>
+      <c r="C56" s="10">
+        <f t="shared" si="1"/>
+        <v>0.27453885975411996</v>
+      </c>
+      <c r="D56" s="11">
+        <f t="shared" si="2"/>
+        <v>0.39212780691254678</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>2.8E-3</v>
+      </c>
+      <c r="B57" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5500000000000003E-3</v>
+      </c>
+      <c r="C57" s="10">
+        <f t="shared" si="1"/>
+        <v>0.27595580227840838</v>
+      </c>
+      <c r="D57" s="11">
+        <f t="shared" si="2"/>
+        <v>0.39071086438825836</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>2.81E-3</v>
+      </c>
+      <c r="B58" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5599999999999999E-3</v>
+      </c>
+      <c r="C58" s="10">
+        <f t="shared" si="1"/>
+        <v>0.277408633812809</v>
+      </c>
+      <c r="D58" s="11">
+        <f t="shared" si="2"/>
+        <v>0.38925803285385774</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>2.82E-3</v>
+      </c>
+      <c r="B59" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5699999999999995E-3</v>
+      </c>
+      <c r="C59" s="10">
+        <f t="shared" si="1"/>
+        <v>0.27890022793815128</v>
+      </c>
+      <c r="D59" s="11">
+        <f t="shared" si="2"/>
+        <v>0.38776643872851546</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>2.8300000000000001E-3</v>
+      </c>
+      <c r="B60" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5799999999999999E-3</v>
+      </c>
+      <c r="C60" s="10">
+        <f t="shared" si="1"/>
+        <v>0.28043386349227489</v>
+      </c>
+      <c r="D60" s="11">
+        <f t="shared" si="2"/>
+        <v>0.38623280317439185</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>2.8400000000000001E-3</v>
+      </c>
+      <c r="B61" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.5900000000000004E-3</v>
+      </c>
+      <c r="C61" s="10">
+        <f t="shared" si="1"/>
+        <v>0.28201330940536634</v>
+      </c>
+      <c r="D61" s="11">
+        <f t="shared" si="2"/>
+        <v>0.3846533572613004</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>2.8500000000000001E-3</v>
+      </c>
+      <c r="B62" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.6E-3</v>
+      </c>
+      <c r="C62" s="10">
+        <f t="shared" si="1"/>
+        <v>0.28364293383333766</v>
+      </c>
+      <c r="D62" s="11">
+        <f t="shared" si="2"/>
+        <v>0.38302373283332908</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <v>2.8600000000000001E-3</v>
+      </c>
+      <c r="B63" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.6099999999999996E-3</v>
+      </c>
+      <c r="C63" s="10">
+        <f t="shared" si="1"/>
+        <v>0.28532784667845984</v>
+      </c>
+      <c r="D63" s="11">
+        <f t="shared" si="2"/>
+        <v>0.3813388199882069</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>2.8700000000000002E-3</v>
+      </c>
+      <c r="B64" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.62E-3</v>
+      </c>
+      <c r="C64" s="10">
+        <f t="shared" si="1"/>
+        <v>0.28707408890075237</v>
+      </c>
+      <c r="D64" s="11">
+        <f t="shared" si="2"/>
+        <v>0.37959257776591437</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
+        <v>2.8800000000000002E-3</v>
+      </c>
+      <c r="B65" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.6300000000000005E-3</v>
+      </c>
+      <c r="C65" s="10">
+        <f t="shared" si="1"/>
+        <v>0.2888888888888887</v>
+      </c>
+      <c r="D65" s="11">
+        <f t="shared" si="2"/>
+        <v>0.37777777777777805</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>2.8900000000000002E-3</v>
+      </c>
+      <c r="B66" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.6400000000000001E-3</v>
+      </c>
+      <c r="C66" s="10">
+        <f t="shared" si="1"/>
+        <v>0.29078101743305135</v>
+      </c>
+      <c r="D66" s="11">
+        <f t="shared" si="2"/>
+        <v>0.37588564923361539</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="8">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="B67" s="3">
+        <f t="shared" ref="B67:B77" si="3">(-5*$I$2/4)-A67</f>
+        <v>-6.6499999999999997E-3</v>
+      </c>
+      <c r="C67" s="10">
+        <f t="shared" ref="C67:C77" si="4">(-$L$2+SQRT(POWER($L$2,2)-(4*$K$2*B67)))/(2*$K$2)</f>
+        <v>0.29276129203665396</v>
+      </c>
+      <c r="D67" s="11">
+        <f t="shared" ref="D67:D77" si="5">(-$L$2-SQRT(POWER($L$2,2)-(4*$K$2*B67)))/(2*$K$2)</f>
+        <v>0.37390537463001278</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>2.9099999999999998E-3</v>
+      </c>
+      <c r="B68" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.6599999999999993E-3</v>
+      </c>
+      <c r="C68" s="10">
+        <f t="shared" si="4"/>
+        <v>0.29484331538735775</v>
+      </c>
+      <c r="D68" s="11">
+        <f t="shared" si="5"/>
+        <v>0.37182335127930899</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <v>2.9199999999999999E-3</v>
+      </c>
+      <c r="B69" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.6699999999999997E-3</v>
+      </c>
+      <c r="C69" s="10">
+        <f t="shared" si="4"/>
+        <v>0.29704459640321168</v>
+      </c>
+      <c r="D69" s="11">
+        <f t="shared" si="5"/>
+        <v>0.36962207026345506</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <v>2.9299999999999999E-3</v>
+      </c>
+      <c r="B70" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.6800000000000002E-3</v>
+      </c>
+      <c r="C70" s="10">
+        <f t="shared" si="4"/>
+        <v>0.29938832818551186</v>
+      </c>
+      <c r="D70" s="11">
+        <f t="shared" si="5"/>
+        <v>0.36727833848115488</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>2.9399999999999999E-3</v>
+      </c>
+      <c r="B71" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.6899999999999998E-3</v>
+      </c>
+      <c r="C71" s="10">
+        <f t="shared" si="4"/>
+        <v>0.30190636528059728</v>
+      </c>
+      <c r="D71" s="11">
+        <f t="shared" si="5"/>
+        <v>0.36476030138606946</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>2.9499999999999999E-3</v>
+      </c>
+      <c r="B72" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.6999999999999994E-3</v>
+      </c>
+      <c r="C72" s="10">
+        <f t="shared" si="4"/>
+        <v>0.30464456780587018</v>
+      </c>
+      <c r="D72" s="11">
+        <f t="shared" si="5"/>
+        <v>0.36202209886079656</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>2.96E-3</v>
+      </c>
+      <c r="B73" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.7099999999999998E-3</v>
+      </c>
+      <c r="C73" s="10">
+        <f t="shared" si="4"/>
+        <v>0.30767332136934922</v>
+      </c>
+      <c r="D73" s="11">
+        <f t="shared" si="5"/>
+        <v>0.35899334529731752</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>2.97E-3</v>
+      </c>
+      <c r="B74" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.7200000000000003E-3</v>
+      </c>
+      <c r="C74" s="10">
+        <f t="shared" si="4"/>
+        <v>0.31111111111111039</v>
+      </c>
+      <c r="D74" s="11">
+        <f t="shared" si="5"/>
+        <v>0.35555555555555635</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>2.98E-3</v>
+      </c>
+      <c r="B75" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.7299999999999999E-3</v>
+      </c>
+      <c r="C75" s="10">
+        <f t="shared" si="4"/>
+        <v>0.31518896486827164</v>
+      </c>
+      <c r="D75" s="11">
+        <f t="shared" si="5"/>
+        <v>0.3514777017983951</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>2.99E-3</v>
+      </c>
+      <c r="B76" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.7399999999999995E-3</v>
+      </c>
+      <c r="C76" s="10">
+        <f t="shared" si="4"/>
+        <v>0.32050332735134029</v>
+      </c>
+      <c r="D76" s="11">
+        <f t="shared" si="5"/>
+        <v>0.3461633393153265</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="B77" s="3">
+        <f t="shared" si="3"/>
+        <v>-6.7499999999999999E-3</v>
+      </c>
+      <c r="C77" s="10">
+        <f t="shared" si="4"/>
+        <v>0.33333332791321396</v>
+      </c>
+      <c r="D77" s="11">
+        <f t="shared" si="5"/>
+        <v>0.33333333875345278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BBB5E9-8FB7-45F6-ABE1-EDC3636E8964}">
   <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
